--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,6 +1061,297 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126125006</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örnbergslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492186</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6828204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126125026</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Örnbergslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492207</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6828185</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126125038</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97223</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Örnbergslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492227</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6828175</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126123795</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126123800</v>
+        <v>126121970</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>91254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492335</v>
+        <v>492635</v>
       </c>
       <c r="R3" t="n">
-        <v>6828021</v>
+        <v>6828171</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126121970</v>
+        <v>126123800</v>
       </c>
       <c r="B4" t="n">
-        <v>91252</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492635</v>
+        <v>492335</v>
       </c>
       <c r="R4" t="n">
-        <v>6828171</v>
+        <v>6828021</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>126122078</v>
       </c>
       <c r="B5" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126125006</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126125026</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126125038</v>
       </c>
       <c r="B8" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126121970</v>
+        <v>126123800</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492635</v>
+        <v>492335</v>
       </c>
       <c r="R3" t="n">
-        <v>6828171</v>
+        <v>6828021</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126123800</v>
+        <v>126121970</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492335</v>
+        <v>492635</v>
       </c>
       <c r="R4" t="n">
-        <v>6828021</v>
+        <v>6828171</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>126122078</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126125006</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126125026</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126125038</v>
       </c>
       <c r="B8" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126121970</v>
       </c>
       <c r="B4" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126122078</v>
       </c>
       <c r="B5" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126125006</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126125026</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126125038</v>
       </c>
       <c r="B8" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126123795</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126123800</v>
+        <v>126121970</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>91262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492335</v>
+        <v>492635</v>
       </c>
       <c r="R3" t="n">
-        <v>6828021</v>
+        <v>6828171</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126121970</v>
+        <v>126123800</v>
       </c>
       <c r="B4" t="n">
-        <v>91258</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492635</v>
+        <v>492335</v>
       </c>
       <c r="R4" t="n">
-        <v>6828171</v>
+        <v>6828021</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>126122078</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126125006</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126125026</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126125038</v>
       </c>
       <c r="B8" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126121970</v>
+        <v>126123800</v>
       </c>
       <c r="B3" t="n">
-        <v>91262</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492635</v>
+        <v>492335</v>
       </c>
       <c r="R3" t="n">
-        <v>6828171</v>
+        <v>6828021</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126123800</v>
+        <v>126121970</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>91262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492335</v>
+        <v>492635</v>
       </c>
       <c r="R4" t="n">
-        <v>6828021</v>
+        <v>6828171</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
         <v>126122078</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126125006</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126125026</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126125038</v>
       </c>
       <c r="B8" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126123800</v>
+        <v>126121970</v>
       </c>
       <c r="B3" t="n">
-        <v>80081</v>
+        <v>91262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492335</v>
+        <v>492635</v>
       </c>
       <c r="R3" t="n">
-        <v>6828021</v>
+        <v>6828171</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126121970</v>
+        <v>126123800</v>
       </c>
       <c r="B4" t="n">
-        <v>91262</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492635</v>
+        <v>492335</v>
       </c>
       <c r="R4" t="n">
-        <v>6828171</v>
+        <v>6828021</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126123795</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126121970</v>
       </c>
       <c r="B3" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126123800</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126122078</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126125006</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126125026</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126125038</v>
       </c>
       <c r="B8" t="n">
-        <v>97236</v>
+        <v>97245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29228-2025 artfynd.xlsx
+++ b/artfynd/A 29228-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126121970</v>
+        <v>126123800</v>
       </c>
       <c r="B3" t="n">
-        <v>91265</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492635</v>
+        <v>492335</v>
       </c>
       <c r="R3" t="n">
-        <v>6828171</v>
+        <v>6828021</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126123800</v>
+        <v>126121970</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>91265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492335</v>
+        <v>492635</v>
       </c>
       <c r="R4" t="n">
-        <v>6828021</v>
+        <v>6828171</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
